--- a/NECP Scenario/Results/Regional Results/EL53_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL53_Generation.xlsx
@@ -537,25 +537,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.547323015759987E-12</v>
+        <v>2.284563472995446E-12</v>
       </c>
       <c r="C2">
-        <v>8.102393478883658E-13</v>
+        <v>1.196285479471242E-12</v>
       </c>
       <c r="D2">
-        <v>1.190475065365407E-12</v>
+        <v>1.757692136999715E-12</v>
       </c>
       <c r="E2">
-        <v>1.749235209984704E-12</v>
+        <v>2.582682488872156E-12</v>
       </c>
       <c r="F2">
-        <v>2.570226168441579E-12</v>
+        <v>3.794844406141468E-12</v>
       </c>
       <c r="G2">
-        <v>3.776453587682308E-12</v>
+        <v>5.575793214327267E-12</v>
       </c>
       <c r="H2">
-        <v>2.288757284823934E-11</v>
+        <v>3.379285157609414E-11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5.400670588630272E-08</v>
+        <v>7.970448753336762E-08</v>
       </c>
       <c r="C3">
-        <v>4.714942997520309E-08</v>
+        <v>6.917355752574356E-08</v>
       </c>
       <c r="D3">
-        <v>1.434394686802303E-07</v>
+        <v>2.046360256861464E-07</v>
       </c>
       <c r="E3">
-        <v>2.912973495062293E-07</v>
+        <v>3.914984335281707E-07</v>
       </c>
       <c r="F3">
-        <v>9.350867318307606E-07</v>
+        <v>1.199531792796258E-06</v>
       </c>
       <c r="G3">
-        <v>5.387125699765173E-06</v>
+        <v>7.339651885525793E-06</v>
       </c>
       <c r="H3">
-        <v>9.717403983332276E-06</v>
+        <v>1.448631342149727E-05</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.590570000642667E-08</v>
+        <v>6.774881440599484E-08</v>
       </c>
       <c r="C4">
-        <v>4.00770154843467E-08</v>
+        <v>5.87975239003179E-08</v>
       </c>
       <c r="D4">
-        <v>1.219235483841157E-07</v>
+        <v>1.739406218370388E-07</v>
       </c>
       <c r="E4">
-        <v>2.47602747086401E-07</v>
+        <v>3.327736685029129E-07</v>
       </c>
       <c r="F4">
-        <v>7.948237220622223E-07</v>
+        <v>1.019602023880765E-06</v>
       </c>
       <c r="G4">
-        <v>4.579056844806487E-06</v>
+        <v>6.238704102700886E-06</v>
       </c>
       <c r="H4">
-        <v>8.259793385838526E-06</v>
+        <v>1.231336640827664E-05</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,22 +618,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.1757314349343733</v>
+        <v>0.175729450548982</v>
       </c>
       <c r="D5">
-        <v>0.1740546278586191</v>
+        <v>0.1738645281987244</v>
       </c>
       <c r="E5">
-        <v>0.2097193817182014</v>
+        <v>0.2096280652366431</v>
       </c>
       <c r="F5">
-        <v>0.2194986297635923</v>
+        <v>0.2200494718841808</v>
       </c>
       <c r="G5">
-        <v>0.2263036687019039</v>
+        <v>0.2263930686176756</v>
       </c>
       <c r="H5">
-        <v>0.2321738906479558</v>
+        <v>0.2324766511323264</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -667,25 +667,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.08661098269238206</v>
+        <v>0.08669937414291885</v>
       </c>
       <c r="C7">
-        <v>0.5880138881255744</v>
+        <v>0.5880138876387834</v>
       </c>
       <c r="D7">
-        <v>0.5728365542698446</v>
+        <v>0.5720406929178975</v>
       </c>
       <c r="E7">
-        <v>0.6719583335289614</v>
+        <v>0.6719583333881235</v>
       </c>
       <c r="F7">
-        <v>0.6956666669661099</v>
+        <v>0.6956666668271568</v>
       </c>
       <c r="G7">
-        <v>0.7103750000773795</v>
+        <v>0.7103749998505066</v>
       </c>
       <c r="H7">
-        <v>0.7250833221808684</v>
+        <v>0.7250833220804754</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -719,25 +719,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.03028356037822404</v>
+        <v>0.03031446647803463</v>
       </c>
       <c r="C9">
-        <v>0.02986782664603578</v>
+        <v>0.02986981086030423</v>
       </c>
       <c r="D9">
-        <v>0.02623787363146269</v>
+        <v>0.02614970009001509</v>
       </c>
       <c r="E9">
-        <v>0.02523108454644653</v>
+        <v>0.02532240097676661</v>
       </c>
       <c r="F9">
-        <v>0.02374146357501853</v>
+        <v>0.02319062140289585</v>
       </c>
       <c r="G9">
-        <v>0.02207919844892911</v>
+        <v>0.02198979844949706</v>
       </c>
       <c r="H9">
-        <v>0.02135174642313659</v>
+        <v>0.02104898587740063</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -748,22 +748,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.138560824742287E-07</v>
+        <v>1.638790787657669E-07</v>
       </c>
       <c r="D10">
-        <v>1.234138809191465E-07</v>
+        <v>1.875437566806866E-07</v>
       </c>
       <c r="E10">
-        <v>1.178832083811772E-07</v>
+        <v>1.760067239039501E-07</v>
       </c>
       <c r="F10">
-        <v>9.124724116161822E-08</v>
+        <v>1.345741471684744E-07</v>
       </c>
       <c r="G10">
-        <v>8.4147311263973E-08</v>
+        <v>1.258322054418155E-07</v>
       </c>
       <c r="H10">
-        <v>3.848683980081353E-07</v>
+        <v>5.740147856157187E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -797,10 +797,10 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>16.43337818897531</v>
+        <v>16.38327037563726</v>
       </c>
       <c r="C12">
-        <v>7.515592030312343</v>
+        <v>7.346740569983874</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>6.559237293278107</v>
+        <v>6.549713936702646</v>
       </c>
       <c r="C13">
-        <v>3.118502917133096</v>
+        <v>3.048440070522965</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.991026653821285</v>
+        <v>0.9910266562485436</v>
       </c>
       <c r="C14">
-        <v>1.006771989441724</v>
+        <v>1.006771988101878</v>
       </c>
       <c r="D14">
-        <v>1.106982198345653</v>
+        <v>1.106982189424303</v>
       </c>
       <c r="E14">
-        <v>1.321978620142547</v>
+        <v>1.321978558751363</v>
       </c>
       <c r="F14">
-        <v>1.600744705335858</v>
+        <v>1.600739937274957</v>
       </c>
       <c r="G14">
-        <v>1.598980635223484</v>
+        <v>1.585276453094349</v>
       </c>
       <c r="H14">
-        <v>2.024380474790159</v>
+        <v>2.024380662178789</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -979,25 +979,25 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4.556742057581359E-08</v>
+        <v>6.729819587782968E-08</v>
       </c>
       <c r="C19">
-        <v>4.328048773826598E-08</v>
+        <v>6.367398234880493E-08</v>
       </c>
       <c r="D19">
-        <v>1.064425104595044E-07</v>
+        <v>1.561189610731956E-07</v>
       </c>
       <c r="E19">
-        <v>2.262657989450307E-07</v>
+        <v>3.145943384338825E-07</v>
       </c>
       <c r="F19">
-        <v>6.154526293756888E-07</v>
+        <v>8.410343270583909E-07</v>
       </c>
       <c r="G19">
-        <v>1.084817681877024E-06</v>
+        <v>1.638684322848702E-06</v>
       </c>
       <c r="H19">
-        <v>3.164119808470654E-06</v>
+        <v>4.785179818305093E-06</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1031,25 +1031,25 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3.645393646470347E-08</v>
+        <v>5.383855670584712E-08</v>
       </c>
       <c r="C21">
-        <v>3.462439019061281E-08</v>
+        <v>5.093918587904392E-08</v>
       </c>
       <c r="D21">
-        <v>8.515400836760354E-08</v>
+        <v>1.248951688585565E-07</v>
       </c>
       <c r="E21">
-        <v>1.810126391560246E-07</v>
+        <v>2.516754707471059E-07</v>
       </c>
       <c r="F21">
-        <v>4.923621035005514E-07</v>
+        <v>6.728274616467133E-07</v>
       </c>
       <c r="G21">
-        <v>8.678541455016198E-07</v>
+        <v>1.310947458278961E-06</v>
       </c>
       <c r="H21">
-        <v>2.531295846776524E-06</v>
+        <v>3.828143854644076E-06</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1060,22 +1060,22 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>1.334316061304219E-08</v>
+        <v>2.020432503041294E-08</v>
       </c>
       <c r="D22">
-        <v>2.013788779040734E-08</v>
+        <v>3.076387684463788E-08</v>
       </c>
       <c r="E22">
-        <v>4.658974508022081E-08</v>
+        <v>7.11344264026004E-08</v>
       </c>
       <c r="F22">
-        <v>1.729301649625337E-07</v>
+        <v>2.528459261992148E-07</v>
       </c>
       <c r="G22">
-        <v>6.732772133424517E-07</v>
+        <v>9.645877672114855E-07</v>
       </c>
       <c r="H22">
-        <v>2.003049091748592E-06</v>
+        <v>3.781511019806334E-06</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1083,25 +1083,25 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.7183840221248593</v>
+        <v>0.7183840220421422</v>
       </c>
       <c r="C23">
-        <v>0.7183840221977946</v>
+        <v>0.7183840221459007</v>
       </c>
       <c r="D23">
-        <v>0.718384022148204</v>
+        <v>0.7183840220787866</v>
       </c>
       <c r="E23">
-        <v>0.7183840221084987</v>
+        <v>0.7183840220174287</v>
       </c>
       <c r="F23">
-        <v>0.718384022046454</v>
+        <v>0.7183840219241173</v>
       </c>
       <c r="G23">
-        <v>0.7183840219229299</v>
+        <v>0.7183840217443693</v>
       </c>
       <c r="H23">
-        <v>0.7183840197775164</v>
+        <v>0.7183840186416725</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1109,25 +1109,25 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.274682214416225E-08</v>
+        <v>1.886680343275412E-08</v>
       </c>
       <c r="C24">
-        <v>1.985150592223611E-07</v>
+        <v>2.859498039742099E-07</v>
       </c>
       <c r="D24">
-        <v>2.140348018413564E-07</v>
+        <v>3.248972627386796E-07</v>
       </c>
       <c r="E24">
-        <v>2.059493931342327E-07</v>
+        <v>3.073029969972039E-07</v>
       </c>
       <c r="F24">
-        <v>1.621958566159189E-07</v>
+        <v>2.391730794074796E-07</v>
       </c>
       <c r="G24">
-        <v>1.527856507233865E-07</v>
+        <v>2.281800012510908E-07</v>
       </c>
       <c r="H24">
-        <v>7.092168914904293E-07</v>
+        <v>1.056891194866097E-06</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1135,25 +1135,25 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>4.572656604734115E-09</v>
+        <v>6.768071497324021E-09</v>
       </c>
       <c r="C25">
-        <v>2.596727351661967E-09</v>
+        <v>3.815215493405832E-09</v>
       </c>
       <c r="D25">
-        <v>2.844295723564195E-09</v>
+        <v>4.194218959507702E-09</v>
       </c>
       <c r="E25">
-        <v>3.677786613610442E-09</v>
+        <v>5.422320716672984E-09</v>
       </c>
       <c r="F25">
-        <v>4.165624405694297E-09</v>
+        <v>6.129751732476539E-09</v>
       </c>
       <c r="G25">
-        <v>4.984887778806208E-09</v>
+        <v>7.349563317468794E-09</v>
       </c>
       <c r="H25">
-        <v>2.788435106675824E-08</v>
+        <v>4.127610068928349E-08</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1268,22 +1268,22 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.05821768789345447</v>
+        <v>2.613712240167353E-06</v>
       </c>
       <c r="D30">
-        <v>0.05718298100398074</v>
+        <v>2.416467412088758E-06</v>
       </c>
       <c r="E30">
-        <v>0.3753769974922932</v>
+        <v>0.2686213895234985</v>
       </c>
       <c r="F30">
-        <v>0.4954763487319049</v>
+        <v>0.3907273834265753</v>
       </c>
       <c r="G30">
-        <v>0.6821984303910823</v>
+        <v>0.5332585936404696</v>
       </c>
       <c r="H30">
-        <v>0.7473641231872791</v>
+        <v>0.619402257470411</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.9507152008365549</v>
+        <v>0.9507151981147359</v>
       </c>
       <c r="C31">
-        <v>0.9507151065177065</v>
+        <v>0.9507150521160186</v>
       </c>
       <c r="D31">
-        <v>0.9462630617249447</v>
+        <v>0.9447610082839931</v>
       </c>
       <c r="E31">
-        <v>0.9339071434132944</v>
+        <v>0.9334575897283811</v>
       </c>
       <c r="F31">
-        <v>0.9243155466251459</v>
+        <v>0.922635661178472</v>
       </c>
       <c r="G31">
-        <v>0.9109682650759736</v>
+        <v>0.9135254441399964</v>
       </c>
       <c r="H31">
-        <v>0.9045218783957704</v>
+        <v>0.9031019705493959</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1320,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>7.158084246095974E-09</v>
+        <v>1.069272362965939E-08</v>
       </c>
       <c r="D32">
-        <v>2.363350231131374E-08</v>
+        <v>3.743273442581408E-08</v>
       </c>
       <c r="E32">
-        <v>7.656274981242356E-08</v>
+        <v>1.447559649009923E-07</v>
       </c>
       <c r="F32">
-        <v>6.111089978100608E-07</v>
+        <v>5.39114880286739E-06</v>
       </c>
       <c r="G32">
-        <v>0.299077864968661</v>
+        <v>0.3128441593534398</v>
       </c>
       <c r="H32">
-        <v>0.3509077486066705</v>
+        <v>0.3509076374963475</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.009906227274181981</v>
+        <v>0.009906224862248868</v>
       </c>
       <c r="C33">
-        <v>0.009906228083662871</v>
+        <v>0.009906225897946786</v>
       </c>
       <c r="D33">
-        <v>0.009906221998330616</v>
+        <v>0.009906217132610778</v>
       </c>
       <c r="E33">
-        <v>0.009906217669810778</v>
+        <v>0.00990621088523558</v>
       </c>
       <c r="F33">
-        <v>0.009906208080397575</v>
+        <v>0.009906196127322874</v>
       </c>
       <c r="G33">
-        <v>0.009579674538965183</v>
+        <v>0.00951756232091077</v>
       </c>
       <c r="H33">
-        <v>0.009714996190754135</v>
+        <v>0.009714920145878853</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>7.75637018455256E-09</v>
+        <v>1.148965845635877E-08</v>
       </c>
       <c r="D34">
-        <v>9.954491212224173E-09</v>
+        <v>1.495192656187177E-08</v>
       </c>
       <c r="E34">
-        <v>1.668084754112869E-08</v>
+        <v>2.508396562127112E-08</v>
       </c>
       <c r="F34">
-        <v>2.56412724447204E-08</v>
+        <v>3.847020946689749E-08</v>
       </c>
       <c r="G34">
-        <v>3.658302840127853E-08</v>
+        <v>5.41088558434323E-08</v>
       </c>
       <c r="H34">
-        <v>2.046281002389379E-07</v>
+        <v>3.078543932149482E-07</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>0.05414637989941015</v>
+        <v>0.0541463798931821</v>
       </c>
       <c r="C35">
-        <v>0.05414637739480038</v>
+        <v>0.0541463761845241</v>
       </c>
       <c r="D35">
-        <v>0.05414637564222254</v>
+        <v>0.0541463732799114</v>
       </c>
       <c r="E35">
-        <v>0.05414613690717855</v>
+        <v>0.05414603525118065</v>
       </c>
       <c r="F35">
-        <v>0.05414596758178383</v>
+        <v>0.05414572245289107</v>
       </c>
       <c r="G35">
-        <v>0.05414568150095135</v>
+        <v>0.05414520976533297</v>
       </c>
       <c r="H35">
-        <v>0.05414024841538589</v>
+        <v>0.05412742261871049</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>4.887517924613989E-08</v>
+        <v>7.321441101265523E-08</v>
       </c>
       <c r="D36">
-        <v>5.281288717175454E-08</v>
+        <v>7.876207454460762E-08</v>
       </c>
       <c r="E36">
-        <v>1.399136353887244E-07</v>
+        <v>2.262926512524497E-07</v>
       </c>
       <c r="F36">
-        <v>2.647093655837847E-07</v>
+        <v>4.118382109478815E-07</v>
       </c>
       <c r="G36">
-        <v>2.628263315183831E-07</v>
+        <v>3.983107194413499E-07</v>
       </c>
       <c r="H36">
-        <v>9.705200920188288E-07</v>
+        <v>1.529724708223859E-06</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.5955592915648124</v>
+        <v>0.5955592864707121</v>
       </c>
       <c r="C37">
-        <v>0.5838078107094511</v>
+        <v>0.5832296166322386</v>
       </c>
       <c r="D37">
-        <v>0.5391909099967729</v>
+        <v>0.5359969821925591</v>
       </c>
       <c r="E37">
-        <v>0.5239392689422272</v>
+        <v>0.5238414399276893</v>
       </c>
       <c r="F37">
-        <v>0.5268152137705489</v>
+        <v>0.519930079562121</v>
       </c>
       <c r="G37">
-        <v>0.5340839618458406</v>
+        <v>0.5350953487612637</v>
       </c>
       <c r="H37">
-        <v>0.5345136843080055</v>
+        <v>0.5283976178784661</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>0.001105050119849998</v>
+        <v>0.001105060353930429</v>
       </c>
       <c r="C38">
-        <v>0.0128567384889328</v>
+        <v>0.01343496013598755</v>
       </c>
       <c r="D38">
-        <v>0.06296040948426092</v>
+        <v>0.06662186948999463</v>
       </c>
       <c r="E38">
-        <v>0.1014115966689275</v>
+        <v>0.09998942701103845</v>
       </c>
       <c r="F38">
-        <v>0.1170231457855167</v>
+        <v>0.1241681681722274</v>
       </c>
       <c r="G38">
-        <v>0.1416921598974005</v>
+        <v>0.1332514014373789</v>
       </c>
       <c r="H38">
-        <v>0.1543831286118957</v>
+        <v>0.1591680360859986</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>9.957412646211632E-08</v>
+        <v>1.470026834111973E-07</v>
       </c>
       <c r="C40">
-        <v>9.042991771346907E-08</v>
+        <v>1.328475398745485E-07</v>
       </c>
       <c r="D40">
-        <v>2.498819791397347E-07</v>
+        <v>3.60754986759342E-07</v>
       </c>
       <c r="E40">
-        <v>5.175631484512601E-07</v>
+        <v>7.060927719620533E-07</v>
       </c>
       <c r="F40">
-        <v>1.550539361206449E-06</v>
+        <v>2.040566119854649E-06</v>
       </c>
       <c r="G40">
-        <v>6.471943381642197E-06</v>
+        <v>8.978336208374495E-06</v>
       </c>
       <c r="H40">
-        <v>1.288152379180293E-05</v>
+        <v>1.927149323980237E-05</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>8.235963647113014E-08</v>
+        <v>1.21587371111842E-07</v>
       </c>
       <c r="C41">
-        <v>7.47014056749595E-08</v>
+        <v>1.097367097793618E-07</v>
       </c>
       <c r="D41">
-        <v>2.070775567517193E-07</v>
+        <v>2.988357906955953E-07</v>
       </c>
       <c r="E41">
-        <v>4.286153862424256E-07</v>
+        <v>5.844491392500188E-07</v>
       </c>
       <c r="F41">
-        <v>1.287185825562774E-06</v>
+        <v>1.692429485527478E-06</v>
       </c>
       <c r="G41">
-        <v>5.446910990308106E-06</v>
+        <v>7.549651560979847E-06</v>
       </c>
       <c r="H41">
-        <v>1.079108923261505E-05</v>
+        <v>1.614151026292072E-05</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-1.721448999098618E-08</v>
+        <v>-2.541531229935535E-08</v>
       </c>
       <c r="C42">
-        <v>-1.572851203850957E-08</v>
+        <v>-2.311083009518667E-08</v>
       </c>
       <c r="D42">
-        <v>-4.280442238801543E-08</v>
+        <v>-6.19191960637467E-08</v>
       </c>
       <c r="E42">
-        <v>-8.894776220883443E-08</v>
+        <v>-1.216436327120344E-07</v>
       </c>
       <c r="F42">
-        <v>-2.633535356436758E-07</v>
+        <v>-3.481366343271709E-07</v>
       </c>
       <c r="G42">
-        <v>-1.025032391334091E-06</v>
+        <v>-1.428684647394647E-06</v>
       </c>
       <c r="H42">
-        <v>-2.09043455918788E-06</v>
+        <v>-3.129982976881651E-06</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1603,25 +1603,25 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>-11.14153897573552</v>
+        <v>-11.12640772500176</v>
       </c>
       <c r="C43">
-        <v>-3.168306774368963</v>
+        <v>-3.0253887978636</v>
       </c>
       <c r="D43">
-        <v>0.7245251862368682</v>
+        <v>0.8133023329966279</v>
       </c>
       <c r="E43">
-        <v>1.353964941957382</v>
+        <v>1.506144373175249</v>
       </c>
       <c r="F43">
-        <v>1.574343846777227</v>
+        <v>1.6806176870088</v>
       </c>
       <c r="G43">
-        <v>1.320785545072091</v>
+        <v>1.564420140136016</v>
       </c>
       <c r="H43">
-        <v>1.450988650437643</v>
+        <v>1.625335133002163</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1629,25 +1629,25 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>3.310678497493775</v>
+        <v>3.304924636813553</v>
       </c>
       <c r="C44">
-        <v>-1.52423288181082</v>
+        <v>-1.538581743955878</v>
       </c>
       <c r="D44">
-        <v>-2.153481156485371</v>
+        <v>-2.180646892973694</v>
       </c>
       <c r="E44">
-        <v>-2.903787181204606</v>
+        <v>-2.949579576553679</v>
       </c>
       <c r="F44">
-        <v>-2.962559560859804</v>
+        <v>-2.955380658405013</v>
       </c>
       <c r="G44">
-        <v>-2.895240731301354</v>
+        <v>-3.009778278447949</v>
       </c>
       <c r="H44">
-        <v>-2.650760591402481</v>
+        <v>-2.690390415879904</v>
       </c>
     </row>
   </sheetData>
